--- a/BaoCao/11.SprintBacklog.xlsx
+++ b/BaoCao/11.SprintBacklog.xlsx
@@ -34,7 +34,7 @@
     <t>Project name:</t>
   </si>
   <si>
-    <t>SMARTTRIAL</t>
+    <t>SmartTrial</t>
   </si>
   <si>
     <t>Kết thúc</t>
@@ -97,7 +97,7 @@
     <t>Sprint</t>
   </si>
   <si>
-    <t>Compoment</t>
+    <t>Component</t>
   </si>
   <si>
     <t>Task name</t>
